--- a/outputs/etf_trend_strategy/threshold_0.7/backtests/window_40/return_vol/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.7/backtests/window_40/return_vol/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
@@ -466,12 +466,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1378507659457715</v>
+        <v>0.1343231706056056</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3093623542370397</v>
+        <v>0.1764568563116119</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.5780428749025028</v>
+        <v>0.8108645768638697</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.8284054408745583</v>
+        <v>1.185007320339847</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2452046154009089</v>
+        <v>0.1248554013307271</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.6407765245230628</v>
+        <v>1.22596478900484</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>40.95732033426001</v>
+        <v>36.02867509952524</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2767571499010425</v>
+        <v>0.1065289077940508</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2458445919451188</v>
+        <v>0.2941064679269002</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.309327116255936</v>
+        <v>0.4537295653420348</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.721120831150954</v>
+        <v>0.6844745315131516</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3345457868325244</v>
+        <v>0.1717263648669227</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8560143822596487</v>
+        <v>0.647350715541929</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>53.80882832874926</v>
+        <v>24.87310906649281</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.0883217876065292</v>
+        <v>0.1252281653164737</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.228062939132965</v>
+        <v>0.2379693737380428</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.4345592488091461</v>
+        <v>0.5721691929230426</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.6494144792004758</v>
+        <v>0.8427382622271832</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1998616080140212</v>
+        <v>0.2277105632068577</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.4609926803518865</v>
+        <v>0.5740952434276934</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>59.00178434054995</v>
+        <v>62.36101735263374</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.04611863388409621</v>
+        <v>0.2334891078635171</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2376020803695761</v>
+        <v>0.2743194017131701</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.2539308559298423</v>
+        <v>0.8791938476537132</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.3564720790112648</v>
+        <v>1.281916447545266</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.157652330260184</v>
+        <v>0.142623429871223</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.304908044188815</v>
+        <v>1.712422991772284</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>54.74641560207831</v>
+        <v>61.5694515623929</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2579336511234291</v>
+        <v>0.2370120677725669</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.248090345286276</v>
+        <v>0.264784004346305</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.023916318027505</v>
+        <v>0.9100995111100426</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.437480994231965</v>
+        <v>1.269137024803198</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2167364673003017</v>
+        <v>0.2129926560028017</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.239617274691605</v>
+        <v>1.1587038282408</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>64.49850210937375</v>
+        <v>67.53073454082985</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.0581636940012209</v>
+        <v>0.6556168790450225</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3282991621959181</v>
+        <v>0.3829189251305538</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.4307822280547918</v>
+        <v>2.541516417497513</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.5942077669847637</v>
+        <v>4.19504890721397</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2117741638203344</v>
+        <v>0.1212515504676857</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.5096559637069314</v>
+        <v>12.32465230262076</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>43.32047090967346</v>
+        <v>40.824640891085</v>
       </c>
     </row>
   </sheetData>
